--- a/inventory_result.xlsx
+++ b/inventory_result.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0099FF99"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,108 +429,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>商品コード</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>現在庫</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>出荷合計</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>1日平均出荷数</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>残り日数</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>リスク</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>JN-CA01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>注意</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>危険</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>JN-CB02</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>問題なし</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>AB-CD03</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>問題なし</t>
         </is>
@@ -536,6 +560,381 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>出荷なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>商品コード</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>現在庫</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>出荷合計</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1日平均出荷数</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>残り日数</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>JN-CA01</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>危険</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>JN-CB02</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>AB-CD03</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XY-ZA04</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>出荷なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>商品コード</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>現在庫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>出荷合計</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1日平均出荷数</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>残り日数</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>JN-CA01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>危険</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>JN-CB02</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>AB-CD03</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>XY-ZA04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>50</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>出荷なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>商品コード</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>現在庫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>出荷合計</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1日平均出荷数</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>残り日数</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>JN-CA01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>危険</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>JN-CB02</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>AB-CD03</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>XY-ZA04</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>出荷なし</t>
         </is>

--- a/inventory_result.xlsx
+++ b/inventory_result.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -565,381 +565,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>商品コード</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>現在庫</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>出荷合計</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1日平均出荷数</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>残り日数</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>リスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>JN-CA01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>危険</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>JN-CB02</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>AB-CD03</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>XY-ZA04</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>50</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>出荷なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>商品コード</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>現在庫</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>出荷合計</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1日平均出荷数</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>残り日数</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>リスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>JN-CA01</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>危険</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>JN-CB02</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>AB-CD03</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>XY-ZA04</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>50</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>出荷なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>商品コード</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>現在庫</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>出荷合計</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1日平均出荷数</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>残り日数</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>リスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>JN-CA01</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>危険</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>JN-CB02</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>AB-CD03</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>問題なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>XY-ZA04</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>50</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>出荷なし</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
